--- a/docs/TestCases_Cien_nad_Arkham.xlsx
+++ b/docs/TestCases_Cien_nad_Arkham.xlsx
@@ -8,7 +8,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="174">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -57,7 +57,7 @@
   </si>
   <si>
     <t xml:space="preserve">1. Plik wczytuje sie bez wyjatku
-2. Gra pokazuje menu glowne</t>
+2. Pojawia sie menu glowne</t>
   </si>
   <si>
     <t xml:space="preserve">Pozytywny</t>
@@ -70,7 +70,7 @@
 2. Sprawdz log w konsoli</t>
   </si>
   <si>
-    <t xml:space="preserve">1. W logu pojawia sie 'Wczytano fabule: 12 wezlow.'</t>
+    <t xml:space="preserve">1. W logu pojawia sie 'Wczytano fabule: 11 wezlow.'</t>
   </si>
   <si>
     <t xml:space="preserve">Brak pliku config.json</t>
@@ -82,7 +82,7 @@
     <t xml:space="preserve">Wysoki</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Tymczasowo zmien nazwe data/config.json na _config.json
+    <t xml:space="preserve">1. Tymczasowo zmien nazwe data/config.json
 2. Uruchom python main.py</t>
   </si>
   <si>
@@ -92,7 +92,7 @@
     <t xml:space="preserve">Brak pliku story.json</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Tymczasowo zmien nazwe data/story.json na _story.json
+    <t xml:space="preserve">1. Tymczasowo zmien nazwe data/story.json
 2. Uruchom python main.py</t>
   </si>
   <si>
@@ -100,8 +100,7 @@
   </si>
   <si>
     <t xml:space="preserve">1. Edytuj story.json - usun jeden zamykajacy nawias }
-2. Uruchom python main.py
-3. Klik START</t>
+2. Uruchom python main.py i kliknij START</t>
   </si>
   <si>
     <t xml:space="preserve">1. Program rzuca wyjatek json.JSONDecodeError
@@ -120,11 +119,11 @@
     <t xml:space="preserve">Sredni</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Edytuj story.json - dodaj wezel z tekstem zawierajacym polskie znaki
-2. Uruchom gre i przejdz do tego wezla</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Tekst wyswietla sie poprawnie z polskimi znakami (zal, czerwony itp.)</t>
+    <t xml:space="preserve">1. Uruchom gre i przejdz do dowolnego wezla
+2. Sprawdz czy polskie znaki (a, e, c, n, o, s, z) renderuja sie poprawnie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Wszystkie polskie znaki sa widoczne bez znakow zastepczych</t>
   </si>
   <si>
     <t xml:space="preserve">Klucz 'tytul' w config.json zachowuje wartosc</t>
@@ -133,18 +132,18 @@
     <t xml:space="preserve">Niski</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Sprawdz w kodzie ze config['tytul'] = 'Cien nad Arkham'
-2. Uruchom engine.py</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. W konsoli widzimy 'Gra: Cien nad Arkham v1.0'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brakujacy klucz 'start_wezel' w config</t>
+    <t xml:space="preserve">1. Uruchom engine.py
+2. Sprawdz pierwsza linie po '=== TEST SILNIKA ==='</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. W konsoli pojawia sie 'Gra: Cien nad Arkham v1.1'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brakujacy klucz 'start_wezel' w config.json</t>
   </si>
   <si>
     <t xml:space="preserve">1. Usun klucz 'start_wezel' z config.json
-2. Uruchom python main.py i kliknij START</t>
+2. Uruchom main.py i kliknij START</t>
   </si>
   <si>
     <t xml:space="preserve">1. Program rzuca wyjatek KeyError</t>
@@ -164,19 +163,18 @@
 2. Gra nie crashuje (zwraca None i konczy plynnie)</t>
   </si>
   <si>
-    <t xml:space="preserve">Format pola 'efekt' (slownik z 'hp' i 'sanity')</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Ustaw w wezle efekt {'hp': -10, 'sanity': -5}
-2. Wejdz do tego wezla
-3. Sprawdz HP i Sanity w GUI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. HP zmniejsza sie o 10
-2. Sanity zmniejsza sie o 5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Inicjalizacja stanu gry z domyslnymi wartosciami</t>
+    <t xml:space="preserve">Format pola 'efekt' aplikuje zmiane HP i Sanity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Z menu START -&gt; intro -&gt; rozdroze
+2. Wybierz 'Zapusc sie do jaskini'
+3. Sprawdz Sanity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Po wejsciu do wezla 'jaskinia' Sanity spada z 100 do 90</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inicjalizacja stanu gry z wartosciami z config</t>
   </si>
   <si>
     <t xml:space="preserve">1. Uruchom python engine.py
@@ -185,94 +183,99 @@
   <si>
     <t xml:space="preserve">1. HP = 100
 2. Sanity = 100
-3. obecny_wezel = 'start'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Przejscie miedzy wezlami przez wybor bez warunku</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Uruchom engine.py
-2. Wpisz '0' (pierwszy wybor: jaskinia)
-3. Sprawdz aktualny wezel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Po wyborze wezel zmienia sie na 'jaskinia'
-2. W konsoli widac 'Przejscie -&gt; jaskinia'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aplikowanie efektu wezla po wejsciu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Z 'start' wybierz 'jaskinia' (efekt sanity -10)
-2. Sprawdz Sanity po przejsciu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Sanity spada ze 100 do 90</t>
+3. obecny_wezel = 'intro'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Przejscie z intro do rozdroze (pierwszy wybor po wstepie)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. START
+2. Kliknij 'Wstajesz i ruszasz w droge'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Wezel zmienia sie na 'rozdroze'
+2. W konsoli widac 'Przejscie -&gt; rozdroze'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aplikowanie efektu wezla po wejsciu (jaskinia)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. START -&gt; rozdroze
+2. Wybierz 'Zapusc sie do jaskini'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Wezel: jaskinia
+2. Sanity spada o 10 (do 90)</t>
   </si>
   <si>
     <t xml:space="preserve">Sprawdzanie warunku rzutu kostka - sukces</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Uruchom test wielokrotnie engine.py i wybierz 'wywaz drzwi'
-2. Pamietaj losowosc
-3. Powtorz az wypadnie SUKCES</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Przy wyniku &gt;= 12 -&gt; przejscie do 'chata'
-2. Brak utraty HP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sprawdzanie warunku rzutu kostka - porazka z cel_porazka</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Uruchom engine.py i wybieraj 'wywaz drzwi' az do PORAZKI (rzut &lt; 12)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Przy wyniku &lt; 12 -&gt; przejscie do 'chata_porazka'
-2. HP spada o 10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sprawdzanie warunku min_hp - niespelniony</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Doprowadz HP gracza do 25 (powtorne wywazanie drzwi)
-2. Idz do 'glebiny'
-3. Wybierz 'walcz'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Warunek min_hp 30 niespelniony
-2. Skok do cel_porazka -&gt; 'ucieczka'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sprawdzanie warunku min_sanity - spelniony</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Z startu idz wprost na 'rozstaje' (sanity 100)
-2. Wybierz 'Zapytaj o droge'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Warunek min_sanity 40 spelniony
-2. Przejscie do 'final_dobry'</t>
+    <t xml:space="preserve">1. START -&gt; rozdroze
+2. Klikaj 'Sprobuj wywazyc drzwi chaty' az do SUKCESU (rzut &gt;= 12)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Przejscie do wezla 'chata'
+2. Brak utraty HP
+3. Pojawia sie info o rzucie i grafika kosci</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sprawdzanie warunku rzutu kostka - porazka (cel_porazka)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. START -&gt; rozdroze
+2. Klikaj 'Sprobuj wywazyc drzwi chaty' az do PORAZKI (rzut &lt; 12)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Przejscie do 'chata_porazka'
+2. HP spada o 10
+3. Pojawia sie info o rzucie i grafika kosci</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Warunek min_sanity niespelniony - skok do cel_porazka (szept)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Doprowadz Sanity ponizej 50 (np. wejdz do jaskini, glebin, wroc do rozdroze powtarzalnie)
+2. Idz na rozstaje
+3. Wybierz 'Zapytaj o droge'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Warunek min_sanity 50 niespelniony
+2. Skok do wezla 'szept' (zamiast final_dobry)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Warunek min_sanity spelniony - przejscie do final_dobry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. START -&gt; rozdroze (Sanity=100)
+2. Wybierz 'Idz lesnym duktem'
+3. Wybierz 'Zapytaj o droge'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Warunek spelniony
+2. Przejscie do final_dobry
+3. Ekran ZWYCIESTWO</t>
   </si>
   <si>
     <t xml:space="preserve">Stan 'odwiedzone' nie zawiera duplikatow</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Z 'start' idz do 'jaskinia', wroc do 'start', znowu idz do 'jaskinia'
-2. Sprawdz stan['odwiedzone']</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Lista odwiedzone zawiera 'start' tylko raz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Funkcja czy_koniec wykrywa 'zakonczone: true'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. W kodzie wywolaj czy_koniec na wezle 'final_dobry'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Funkcja zwraca True
-2. Dla pozostalych wezlow zwraca False</t>
+    <t xml:space="preserve">1. Idz intro -&gt; rozdroze -&gt; jaskinia -&gt; wroc do rozdroze -&gt; jaskinia
+2. Wydrukuj stan['odwiedzone']</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Lista zawiera kazdy wezel tylko raz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Funkcja czy_koniec wykrywa flage 'zakonczone: true'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Wywolaj czy_koniec(fabula['final_dobry'])
+2. Wywolaj czy_koniec(fabula['intro'])</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Dla final_dobry zwraca True
+2. Dla intro zwraca False</t>
   </si>
   <si>
     <t xml:space="preserve">Pobranie nieistniejacego wezla zwraca None</t>
@@ -293,8 +296,7 @@
 2. Sprawdz min/max</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Wszystkie wyniki sa w przedziale 1..20
-2. Zaden wynik nie jest 0 ani 21</t>
+    <t xml:space="preserve">1. Wszystkie wyniki w przedziale 1..20</t>
   </si>
   <si>
     <t xml:space="preserve">rzut_koscia(6) zwraca liczbe 1..6</t>
@@ -304,7 +306,7 @@
 2. Sprawdz min/max</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Wszystkie wyniki sa w przedziale 1..6</t>
+    <t xml:space="preserve">1. Wszystkie wyniki w przedziale 1..6</t>
   </si>
   <si>
     <t xml:space="preserve">rzut_koscia bez argumentu uzywa domyslnie k20</t>
@@ -343,7 +345,7 @@
     <t xml:space="preserve">1. Wywolaj sprawdz_rzut(12, 12)</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Funkcja zwraca True (&gt;= a nie &gt;)</t>
+    <t xml:space="preserve">1. Funkcja zwraca True (warunek wynik &gt;= prog, nie &gt;)</t>
   </si>
   <si>
     <t xml:space="preserve">aktualizuj_stan z efektem hp -10</t>
@@ -392,20 +394,20 @@
     <t xml:space="preserve">1. Uruchom python main.py</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Otwiera sie okno tytulu 'Cien nad Arkham'
-2. Widac napis 'CIEN NAD ARKHAM'
+    <t xml:space="preserve">1. Otwiera sie okno 'Cien nad Arkham'
+2. Widac napis CIEN NAD ARKHAM
 3. Widac przyciski START i WYJSCIE</t>
   </si>
   <si>
-    <t xml:space="preserve">Klikniecie START przelacza na ekran gry</t>
+    <t xml:space="preserve">Klikniecie START przelacza na ekran gry z wstepem fabularnym</t>
   </si>
   <si>
     <t xml:space="preserve">1. W menu glownym kliknij START</t>
   </si>
   <si>
     <t xml:space="preserve">1. Menu znika
-2. Pojawia sie tekst pierwszej sceny
-3. Widac przyciski wyborow</t>
+2. Pojawia sie tekst wstepu (intro)
+3. Widac jeden przycisk 'Wstajesz i ruszasz w droge'</t>
   </si>
   <si>
     <t xml:space="preserve">Wyswietlanie HP i Sanity na pasku statystyk</t>
@@ -418,54 +420,55 @@
 2. Widac 'Sanity: 100' w kolorze niebieskim</t>
   </si>
   <si>
-    <t xml:space="preserve">Aktualizacja HP po stracie - kolor czerwony przy &lt;30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Doprowadz HP do 25 (kilkukrotne wywazanie drzwi)
+    <t xml:space="preserve">Aktualizacja HP po stracie - kolor czerwony przy &lt; 30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Doprowadz HP do 25 (kilkukrotne nieudane wywazanie drzwi chaty)
 2. Sprawdz kolor etykiety HP</t>
   </si>
   <si>
     <t xml:space="preserve">1. Etykieta HP ma kolor czerwony (#e05555)</t>
   </si>
   <si>
-    <t xml:space="preserve">Wyswietlanie obrazka sceny (PNG)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Wrzuc plik assets/start.png (300x200)
-2. Uruchom gre i kliknij START</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Nad tekstem sceny pojawia sie obrazek
+    <t xml:space="preserve">Wyswietlanie obrazka sceny (PNG z folderu tiles/)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. START
+2. Sprawdz obrazek nad tekstem wstepu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Pojawia sie grafika tiles/camp.png
 2. Tekst sceny widoczny pod obrazkiem</t>
   </si>
   <si>
     <t xml:space="preserve">Brak pliku obrazka - graceful fallback</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Upewnij sie ze assets/start.png nie istnieje
+    <t xml:space="preserve">1. Tymczasowo przenies tiles/camp.png poza folder
 2. Uruchom gre i kliknij START</t>
   </si>
   <si>
     <t xml:space="preserve">1. Brak crashu
 2. Tekst sceny i przyciski sa widoczne
-3. Nie ma pustego pola po obrazku</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Niepoprawny PNG - graceful fallback</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Wrzuc plik assets/start.png ktory nie jest PNG (np. txt zmieniony na .png)
-2. Uruchom gre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Brak crashu
-2. Pole obrazka jest schowane</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Klikniecie wyboru wykonuje przejscie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. W ekranie gry kliknij pierwszy wybor</t>
+3. Pole obrazka jest schowane</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wyswietlanie wyniku rzutu kostka (grafika kosci + tekst)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. START -&gt; rozdroze
+2. Kliknij 'Sprobuj wywazyc drzwi chaty'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Pojawia sie grafika tiles/dice_roll.png
+2. Pojawia sie tekst typu 'Rzut k20: 14 / prog: 12 -&gt; SUKCES'
+3. Po kolejnym wyborze grafika znika</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Klikniecie wyboru wykonuje przejscie miedzy wezlami</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. W ekranie gry kliknij dowolny wybor</t>
   </si>
   <si>
     <t xml:space="preserve">1. Tekst sceny zmienia sie na nastepny wezel
@@ -475,64 +478,91 @@
     <t xml:space="preserve">Ekran konca - zwyciestwo (kolor zielony)</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Przejdz cala gre szczesliwa sciezka do final_dobry</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Pojawia sie naglowek 'ZWYCIESTWO' w kolorze zielonym
-2. Widac przyciski 'Zagraj ponownie' i 'Wroc do menu'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ekran konca - przegrana (kolor czerwony)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Doprowadz HP do 0 (kilkukrotne wywazanie drzwi)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Pojawia sie naglowek 'KONIEC GRY' w kolorze czerwonym
-2. Widac przyciski 'Zagraj ponownie' i 'Wroc do menu'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pelny przebieg gry - sciezka happy path do final_dobry</t>
+    <t xml:space="preserve">1. Przejdz cala gre szczesliwa sciezka do final_dobry
+2. Sprawdz ekran konca</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Pojawia sie grafika tiles/win.png
+2. Naglowek 'ZWYCIESTWO' w kolorze zielonym
+3. Widac przyciski 'Zagraj ponownie' i 'Wroc do menu'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ekran konca - przegrana fabularna (kolor czerwony)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. START -&gt; rozdroze -&gt; rozstaje -&gt; 'Rzuc sie z piesciami'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Wezel atak_potwora pokazuje grafike tiles/wolf.png
+2. Naglowek 'KONIEC GRY' w kolorze czerwonym
+3. HP = 0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pelny przebieg - happy path przez chate (rzut sukces)</t>
   </si>
   <si>
     <t xml:space="preserve">Test integracyjny</t>
   </si>
   <si>
     <t xml:space="preserve">1. START
-2. Idz prosto do rozstaji
-3. Zapytaj o droge</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Gra konczy sie ekranem ZWYCIESTWO
-2. HP &gt; 0, Sanity &gt; 40</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pelny przebieg gry - sciezka final_zly przez atak</t>
+2. intro -&gt; rozdroze
+3. 'Sprobuj wywazyc drzwi chaty' az do SUKCESU
+4. 'Wyrusz droga wskazana na mapie'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Gra konczy sie ZWYCIESTWEM
+2. HP &gt; 0, Sanity &gt; 0
+3. Grafika win.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pelny przebieg - happy path przez rozstaje</t>
   </si>
   <si>
     <t xml:space="preserve">1. START
-2. Idz na rozstaje dowolna sciezka
-3. Wybierz 'Zaatakuj'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Gra konczy sie ekranem KONIEC GRY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pelny przebieg - smierc przez 0 HP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. START
-2. Wywazaj drzwi powtarzalnie az HP spadnie do 0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Gra natychmiast konczy sie ekranem KONIEC GRY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pelny przebieg - smierc przez 0 Sanity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. START
-2. jaskinia (-10) -&gt; back -&gt; jaskinia... powtorz az Sanity = 0</t>
+2. intro -&gt; rozdroze -&gt; 'Idz lesnym duktem'
+3. 'Zapytaj o droge'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Gra konczy sie ZWYCIESTWEM
+2. Sanity = 100 (warunek min 50 spelniony)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Utrata calosci sanity jednym wyborem (wpatrz sie w oczy)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. START -&gt; rozdroze -&gt; jaskinia -&gt; glebiny
+2. Wybierz 'Wpatrz sie w te oczy'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Przejscie do final_szalenstwo
+2. Sanity = 0
+3. Ekran KONIEC GRY z grafika gone_mad.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Utrata calosci hp jednym wyborem (atak na starca)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. START -&gt; rozdroze -&gt; rozstaje
+2. Wybierz 'Rzuc sie na niego z piesciami'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Przejscie do atak_potwora
+2. HP = 0
+3. Ekran KONIEC GRY z grafika wolf.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sciezka szept - nieudany test sanity prowadzi do szalenstwa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Doprowadz Sanity ponizej 50 (kilka wejsc do jaskini i glebin)
+2. Idz do rozstaje
+3. Wybierz 'Zapytaj o droge'
+4. Kliknij dalej w wezle 'szept'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Skok do szept (cel_porazka)
+2. Sanity spada o 30
+3. Po przycisku - final_szalenstwo</t>
   </si>
   <si>
     <t xml:space="preserve">Restart gry przyciskiem 'Zagraj ponownie'</t>
@@ -542,8 +572,8 @@
 2. Kliknij 'Zagraj ponownie'</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Stan resetuje sie do startowego (HP=100, Sanity=100)
-2. Gra zaczyna od wezla 'start'</t>
+    <t xml:space="preserve">1. Stan resetuje sie (HP=100, Sanity=100)
+2. Gra zaczyna od wezla 'intro'</t>
   </si>
   <si>
     <t xml:space="preserve">Powrot do menu z trwajacej gry</t>
@@ -564,17 +594,6 @@
   <si>
     <t xml:space="preserve">1. Okno zamyka sie
 2. Proces Pythona konczy sie czysto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wszystkie 12 wezlow jest osiagalnych</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Zagraj wielokrotnie roznymi sciezkami
-2. Pokrec wybory rzutow kostka
-3. Sprawdz ze odwiedzone byly wszystkie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Kazdy z 12 wezlow ma sciezke prowadzaca do niego</t>
   </si>
   <si>
     <t xml:space="preserve">Test kompatybilnosci na Windows 10</t>
@@ -592,7 +611,8 @@
   </si>
   <si>
     <t xml:space="preserve">1. Gra wstaje bez bledow
-2. Tkinter renderuje okno poprawnie</t>
+2. Tkinter renderuje okno
+3. Polskie znaki widoczne</t>
   </si>
   <si>
     <t xml:space="preserve">Test kompatybilnosci na Linux (Ubuntu/Mint)</t>
@@ -1561,7 +1581,7 @@
         <v>12</v>
       </c>
       <c r="E36" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="F36" t="s">
         <v>124</v>
@@ -1607,13 +1627,13 @@
         <v>129</v>
       </c>
       <c r="C38" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="D38" t="s">
         <v>12</v>
       </c>
       <c r="E38" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="F38" t="s">
         <v>130</v>
@@ -1769,7 +1789,7 @@
         <v>12</v>
       </c>
       <c r="E44" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="F44" t="s">
         <v>149</v>
@@ -1795,13 +1815,13 @@
         <v>12</v>
       </c>
       <c r="E45" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="F45" t="s">
         <v>152</v>
       </c>
       <c r="G45" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="H45" t="s">
         <v>16</v>
@@ -1812,7 +1832,7 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C46" t="s">
         <v>142</v>
@@ -1824,10 +1844,10 @@
         <v>22</v>
       </c>
       <c r="F46" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="G46" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H46" t="s">
         <v>16</v>
@@ -1838,7 +1858,7 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C47" t="s">
         <v>142</v>
@@ -1847,13 +1867,13 @@
         <v>12</v>
       </c>
       <c r="E47" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="F47" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G47" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H47" t="s">
         <v>16</v>
@@ -1864,7 +1884,7 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C48" t="s">
         <v>142</v>
@@ -1876,10 +1896,10 @@
         <v>33</v>
       </c>
       <c r="F48" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G48" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H48" t="s">
         <v>16</v>
@@ -1890,7 +1910,7 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C49" t="s">
         <v>142</v>
@@ -1899,13 +1919,13 @@
         <v>12</v>
       </c>
       <c r="E49" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="F49" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="G49" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H49" t="s">
         <v>16</v>
@@ -1916,22 +1936,22 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C50" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D50" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E50" t="s">
         <v>13</v>
       </c>
       <c r="F50" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="G50" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H50" t="s">
         <v>16</v>
@@ -1942,22 +1962,22 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
+        <v>171</v>
+      </c>
+      <c r="C51" t="s">
+        <v>167</v>
+      </c>
+      <c r="D51" t="s">
+        <v>172</v>
+      </c>
+      <c r="E51" t="s">
+        <v>13</v>
+      </c>
+      <c r="F51" t="s">
+        <v>173</v>
+      </c>
+      <c r="G51" t="s">
         <v>170</v>
-      </c>
-      <c r="C51" t="s">
-        <v>166</v>
-      </c>
-      <c r="D51" t="s">
-        <v>171</v>
-      </c>
-      <c r="E51" t="s">
-        <v>13</v>
-      </c>
-      <c r="F51" t="s">
-        <v>172</v>
-      </c>
-      <c r="G51" t="s">
-        <v>169</v>
       </c>
       <c r="H51" t="s">
         <v>16</v>
